--- a/run_data/mem_time_results_analysed.xlsx
+++ b/run_data/mem_time_results_analysed.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,16 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FMI\semester_2\Parallel_Programming_Python\primes\run_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{DAB3A92D-522F-4227-896C-59938A48B71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4920F0E8-8348-43CD-A21F-A9D2371FF8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3570" yWindow="-20325" windowWidth="26970" windowHeight="19065"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mem_time_results_2026-07-02T19-" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -26,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="58">
   <si>
     <t>serial_bitarray_sieve</t>
   </si>
@@ -118,17 +127,104 @@
   </si>
   <si>
     <t>run3 raw</t>
+  </si>
+  <si>
+    <t>Earlier runs and ral data:</t>
+  </si>
+  <si>
+    <t>function</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>run_date</t>
+  </si>
+  <si>
+    <t>time_avg</t>
+  </si>
+  <si>
+    <t>time_std</t>
+  </si>
+  <si>
+    <t>mem_avg</t>
+  </si>
+  <si>
+    <t>mem_std</t>
+  </si>
+  <si>
+    <t>time_rep_0</t>
+  </si>
+  <si>
+    <t>time_rep_1</t>
+  </si>
+  <si>
+    <t>time_rep_2</t>
+  </si>
+  <si>
+    <t>time_rep_3</t>
+  </si>
+  <si>
+    <t>time_rep_4</t>
+  </si>
+  <si>
+    <t>mem_rep_0</t>
+  </si>
+  <si>
+    <t>mem_rep_1</t>
+  </si>
+  <si>
+    <t>mem_rep_2</t>
+  </si>
+  <si>
+    <t>mem_rep_3</t>
+  </si>
+  <si>
+    <t>mem_rep_4</t>
+  </si>
+  <si>
+    <t>serial_int_array_sieve_no_return</t>
+  </si>
+  <si>
+    <t>2026-07-02T20:47:14</t>
+  </si>
+  <si>
+    <t>serial_bitarray_sieve_no_return</t>
+  </si>
+  <si>
+    <t>serial_bool_sieve_no_return</t>
+  </si>
+  <si>
+    <t>memory [MB]</t>
+  </si>
+  <si>
+    <t>time [s]</t>
+  </si>
+  <si>
+    <t>Slow down (versus bitarray)</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>bit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bool </t>
+  </si>
+  <si>
+    <t>byte</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="172" formatCode="0.000E+00"/>
-    <numFmt numFmtId="174" formatCode="0E+00"/>
+    <numFmt numFmtId="166" formatCode="0.000E+00"/>
+    <numFmt numFmtId="167" formatCode="0E+00"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -273,7 +369,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -459,6 +555,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -635,11 +743,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -652,30 +760,42 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -813,11 +933,11 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'mem_time_results_2026-07-02T19-'!$K$42:$K$44</c:f>
+              <c:f>'mem_time_results_2026-07-02T19-'!$K$44:$K$46</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
+                <c:pt idx="0" formatCode="0">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -831,7 +951,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'mem_time_results_2026-07-02T19-'!$L$42:$L$44</c:f>
+              <c:f>'mem_time_results_2026-07-02T19-'!$L$44:$L$46</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
@@ -839,10 +959,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7581504298989483</c:v>
+                  <c:v>0.56877954411300069</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.459558417764109</c:v>
+                  <c:v>0.68513872951511967</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -883,11 +1003,11 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'mem_time_results_2026-07-02T19-'!$K$42:$K$44</c:f>
+              <c:f>'mem_time_results_2026-07-02T19-'!$K$44:$K$46</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
+                <c:pt idx="0" formatCode="0">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -901,7 +1021,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'mem_time_results_2026-07-02T19-'!$M$42:$M$44</c:f>
+              <c:f>'mem_time_results_2026-07-02T19-'!$M$44:$M$46</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
@@ -909,10 +1029,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.6666636194811135</c:v>
+                  <c:v>0.60000109698880477</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.6341522352780768</c:v>
+                  <c:v>0.61193809145317124</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -953,11 +1073,11 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'mem_time_results_2026-07-02T19-'!$K$42:$K$44</c:f>
+              <c:f>'mem_time_results_2026-07-02T19-'!$K$44:$K$46</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
+                <c:pt idx="0" formatCode="0">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -971,7 +1091,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'mem_time_results_2026-07-02T19-'!$N$42:$N$44</c:f>
+              <c:f>'mem_time_results_2026-07-02T19-'!$N$44:$N$46</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
@@ -979,10 +1099,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.6409013202512253</c:v>
+                  <c:v>0.6094211685117652</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.59277186875099</c:v>
+                  <c:v>0.62783630199607554</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1023,11 +1143,11 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'mem_time_results_2026-07-02T19-'!$K$42:$K$44</c:f>
+              <c:f>'mem_time_results_2026-07-02T19-'!$K$44:$K$46</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0">
+                <c:pt idx="0" formatCode="0">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -1041,7 +1161,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'mem_time_results_2026-07-02T19-'!$O$42:$O$44</c:f>
+              <c:f>'mem_time_results_2026-07-02T19-'!$O$44:$O$46</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1049,10 +1169,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.5560581024947864</c:v>
+                  <c:v>0.64264952471679992</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5765176785365063</c:v>
+                  <c:v>0.63430941093429904</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1096,7 +1216,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1251,7 +1371,664 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.8789370078740155E-2"/>
+          <c:y val="5.0925925925925923E-2"/>
+          <c:w val="0.85287729658792655"/>
+          <c:h val="0.79968953621080319"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>bitarray</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'mem_time_results_2026-07-02T19-'!$D$38:$D$41</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6.2550399999999939</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12.510451199999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24.986047999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>37.564864</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'mem_time_results_2026-07-02T19-'!$E$38:$E$41</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.7516013150000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.05151787</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.308080289999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>32.488548989999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B15F-4A19-A6C0-D761D4C4E4DF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>bool</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'mem_time_results_2026-07-02T19-'!$D$42:$D$45</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>50.123199999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100.11160319999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200.01304319999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>300.06767360000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'mem_time_results_2026-07-02T19-'!$E$42:$E$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8.354029894</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.752499149999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>34.964457080000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50.554069900000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B15F-4A19-A6C0-D761D4C4E4DF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>int</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'mem_time_results_2026-07-02T19-'!$D$46:$D$49</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>399.98467840000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>799.98856960000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1599.9873407999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2400.0237951999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'mem_time_results_2026-07-02T19-'!$E$46:$E$49</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6.9352396970000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.425710389999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>33.938910870000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>51.218771840000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-B15F-4A19-A6C0-D761D4C4E4DF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="362147040"/>
+        <c:axId val="362159520"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="362147040"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>memory [MB]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.75770013123359581"/>
+              <c:y val="0.90690880414209385"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="362159520"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="362159520"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>time [s]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.0173376215297039E-3"/>
+              <c:y val="0.14886467398514872"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="362147040"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.77919303394162354"/>
+          <c:y val="0.60629594104086759"/>
+          <c:w val="0.15633124599582532"/>
+          <c:h val="0.23893968105550256"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1807,19 +2584,535 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1840,6 +3133,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1038225</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCC9A3FA-9BA8-4779-BEBD-8EE35883A342}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2144,8 +3473,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O44"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
@@ -2157,948 +3486,2055 @@
     <col min="7" max="7" width="14.28515625" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
     <col min="9" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" customWidth="1"/>
-    <col min="12" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="9.28515625" customWidth="1"/>
+    <col min="16" max="20" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B1" s="19" t="s">
+    <row r="1" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I2" s="18" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="K2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2"/>
+      <c r="Q2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2"/>
+      <c r="T2" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2" t="s">
+        <v>39</v>
+      </c>
+      <c r="W2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B3" s="19">
         <v>100000</v>
       </c>
-      <c r="C2" s="21">
-        <f>B2/8/10^5</f>
+      <c r="C3" s="20">
+        <f>B3/8/10^5</f>
         <v>0.125</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D3" s="21">
         <v>142677.33333333299</v>
       </c>
-      <c r="E2" s="23">
-        <f>D2/(1.3*B2/8)</f>
+      <c r="E3" s="22">
+        <f>D3/(1.3*B3/8)</f>
         <v>8.7801435897435685</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F3" s="21">
         <v>233472</v>
       </c>
-      <c r="G2" s="24">
-        <f>F2/D2</f>
+      <c r="G3" s="23">
+        <f>F3/D3</f>
         <v>1.6363636363636402</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H3" s="21">
         <v>1101141.33333333</v>
       </c>
-      <c r="I2" s="24">
-        <f>H2/D2</f>
+      <c r="I3" s="23">
+        <f>H3/D3</f>
         <v>7.7177033492822913</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="20">
+      <c r="K3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3">
+        <v>50000000</v>
+      </c>
+      <c r="M3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3">
+        <v>6.9352396970000001</v>
+      </c>
+      <c r="O3">
+        <v>0.118210922</v>
+      </c>
+      <c r="P3" s="31">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="Q3">
+        <v>436184678.39999998</v>
+      </c>
+      <c r="R3">
+        <v>53058.617059999997</v>
+      </c>
+      <c r="S3" s="31">
+        <v>1E-4</v>
+      </c>
+      <c r="T3">
+        <v>7.1157839300000001</v>
+      </c>
+      <c r="U3">
+        <v>6.8581421379999998</v>
+      </c>
+      <c r="V3">
+        <v>6.8468685149999997</v>
+      </c>
+      <c r="W3">
+        <v>6.9963748460000001</v>
+      </c>
+      <c r="X3">
+        <v>6.8590290549999997</v>
+      </c>
+      <c r="Y3">
+        <v>436252672</v>
+      </c>
+      <c r="Z3">
+        <v>436195328</v>
+      </c>
+      <c r="AA3">
+        <v>436109312</v>
+      </c>
+      <c r="AB3">
+        <v>436203520</v>
+      </c>
+      <c r="AC3">
+        <v>436162560</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="19">
         <v>1000000</v>
       </c>
-      <c r="C3" s="21">
-        <f t="shared" ref="C3:C15" si="0">B3/8/10^5</f>
+      <c r="C4" s="20">
+        <f t="shared" ref="C4:C16" si="0">B4/8/10^5</f>
         <v>1.25</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D4" s="21">
         <v>690176</v>
       </c>
-      <c r="E3" s="23">
-        <f>D3/(1.3*B3/8)</f>
+      <c r="E4" s="22">
+        <f>D4/(1.3*B4/8)</f>
         <v>4.2472369230769234</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F4" s="21">
         <v>1701205.33333333</v>
       </c>
-      <c r="G3" s="24">
-        <f>F3/D3</f>
+      <c r="G4" s="23">
+        <f>F4/D4</f>
         <v>2.4648862512363947</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H4" s="21">
         <v>763221.33333333302</v>
       </c>
-      <c r="I3" s="24">
-        <f>H3/D3</f>
+      <c r="I4" s="23">
+        <f>H4/D4</f>
         <v>1.1058358061325415</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="20">
+      <c r="K4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L4">
+        <v>100000000</v>
+      </c>
+      <c r="M4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4">
+        <v>16.425710389999999</v>
+      </c>
+      <c r="O4">
+        <v>1.066537624</v>
+      </c>
+      <c r="P4" s="31">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="Q4">
+        <v>836188569.60000002</v>
+      </c>
+      <c r="R4">
+        <v>107147.79</v>
+      </c>
+      <c r="S4" s="31">
+        <v>1E-4</v>
+      </c>
+      <c r="T4">
+        <v>14.93793273</v>
+      </c>
+      <c r="U4">
+        <v>17.638382199999999</v>
+      </c>
+      <c r="V4">
+        <v>15.84220743</v>
+      </c>
+      <c r="W4">
+        <v>16.57494831</v>
+      </c>
+      <c r="X4">
+        <v>17.135081289999999</v>
+      </c>
+      <c r="Y4">
+        <v>836263936</v>
+      </c>
+      <c r="Z4">
+        <v>836018176</v>
+      </c>
+      <c r="AA4">
+        <v>836210688</v>
+      </c>
+      <c r="AB4">
+        <v>836288512</v>
+      </c>
+      <c r="AC4">
+        <v>836161536</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="19">
         <v>10000000</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C5" s="20">
         <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D5" s="21">
         <v>6113280</v>
       </c>
-      <c r="E4" s="23">
-        <f>D4/(1.3*B4/8)</f>
+      <c r="E5" s="22">
+        <f>D5/(1.3*B5/8)</f>
         <v>3.7620184615384615</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F5" s="21">
         <v>4707669.3333333302</v>
       </c>
-      <c r="G4" s="24">
-        <f>F4/D4</f>
+      <c r="G5" s="23">
+        <f>F5/D5</f>
         <v>0.77007258514796151</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H5" s="21">
         <v>4808704</v>
       </c>
-      <c r="I4" s="24">
-        <f>H4/D4</f>
+      <c r="I5" s="23">
+        <f>H5/D5</f>
         <v>0.78659966499162481</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="20">
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5">
+        <v>200000000</v>
+      </c>
+      <c r="M5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5">
+        <v>33.938910870000001</v>
+      </c>
+      <c r="O5">
+        <v>2.4539336829999998</v>
+      </c>
+      <c r="P5" s="31">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="Q5">
+        <v>1636187341</v>
+      </c>
+      <c r="R5">
+        <v>47714.444470000002</v>
+      </c>
+      <c r="S5" s="31">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>33.453823329999999</v>
+      </c>
+      <c r="U5">
+        <v>37.843404769999999</v>
+      </c>
+      <c r="V5">
+        <v>34.489281890000001</v>
+      </c>
+      <c r="W5">
+        <v>31.493422030000001</v>
+      </c>
+      <c r="X5">
+        <v>32.414622309999999</v>
+      </c>
+      <c r="Y5">
+        <v>1636237312</v>
+      </c>
+      <c r="Z5">
+        <v>1636147200</v>
+      </c>
+      <c r="AA5">
+        <v>1636151296</v>
+      </c>
+      <c r="AB5">
+        <v>1636159488</v>
+      </c>
+      <c r="AC5">
+        <v>1636241408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="19">
         <v>100000000</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C6" s="20">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D6" s="21">
         <v>45580970.666666597</v>
       </c>
-      <c r="E5" s="23">
-        <f>D5/(1.3*B5/8)</f>
+      <c r="E6" s="22">
+        <f>D6/(1.3*B6/8)</f>
         <v>2.8049828102564058</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F6" s="21">
         <v>45529770.666666597</v>
       </c>
-      <c r="G5" s="24">
-        <f>F5/D5</f>
+      <c r="G6" s="23">
+        <f>F6/D6</f>
         <v>0.99887672422830953</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H6" s="21">
         <v>45539328</v>
       </c>
-      <c r="I5" s="24">
-        <f>H5/D5</f>
+      <c r="I6" s="23">
+        <f>H6/D6</f>
         <v>0.99908640237235991</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="24"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="K6" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6">
+        <v>300000000</v>
+      </c>
+      <c r="M6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6">
+        <v>51.218771840000002</v>
+      </c>
+      <c r="O6">
+        <v>2.3979226169999999</v>
+      </c>
+      <c r="P6" s="31">
+        <v>4.7E-2</v>
+      </c>
+      <c r="Q6">
+        <v>2436223795</v>
+      </c>
+      <c r="R6">
+        <v>121762.1689</v>
+      </c>
+      <c r="S6" s="31">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>55.170304299999998</v>
+      </c>
+      <c r="U6">
+        <v>51.053690199999998</v>
+      </c>
+      <c r="V6">
+        <v>48.841680050000001</v>
+      </c>
+      <c r="W6">
+        <v>51.111820940000001</v>
+      </c>
+      <c r="X6">
+        <v>49.91636372</v>
+      </c>
+      <c r="Y6">
+        <v>2436370432</v>
+      </c>
+      <c r="Z6">
+        <v>2436263936</v>
+      </c>
+      <c r="AA6">
+        <v>2436276224</v>
+      </c>
+      <c r="AB6">
+        <v>2436055040</v>
+      </c>
+      <c r="AC6">
+        <v>2436153344</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="23"/>
+      <c r="K7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7">
+        <v>50000000</v>
+      </c>
+      <c r="M7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7">
+        <v>4.7516013150000003</v>
+      </c>
+      <c r="O7">
+        <v>0.358233423</v>
+      </c>
+      <c r="P7" s="31">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="Q7">
+        <v>42455040</v>
+      </c>
+      <c r="R7">
+        <v>161363.6862</v>
+      </c>
+      <c r="S7" s="31">
+        <v>3.8E-3</v>
+      </c>
+      <c r="T7">
+        <v>4.6272280219999997</v>
+      </c>
+      <c r="U7">
+        <v>4.7023365500000001</v>
+      </c>
+      <c r="V7">
+        <v>4.5111644269999998</v>
+      </c>
+      <c r="W7">
+        <v>5.3780968189999996</v>
+      </c>
+      <c r="X7">
+        <v>4.5391807560000004</v>
+      </c>
+      <c r="Y7">
+        <v>42565632</v>
+      </c>
+      <c r="Z7">
+        <v>42557440</v>
+      </c>
+      <c r="AA7">
+        <v>42414080</v>
+      </c>
+      <c r="AB7">
+        <v>42188800</v>
+      </c>
+      <c r="AC7">
+        <v>42549248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B8" s="25">
         <v>100000</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C8" s="20">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D8" s="25">
         <v>35703466.666666597</v>
       </c>
-      <c r="E7" s="23">
-        <f>D7/(1.3*B7/8)</f>
+      <c r="E8" s="22">
+        <f>D8/(1.3*B8/8)</f>
         <v>2197.1364102564062</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F8" s="25">
         <v>35814058.666666597</v>
       </c>
-      <c r="G7" s="24">
-        <f t="shared" ref="G7:G15" si="1">F7/D7</f>
+      <c r="G8" s="23">
+        <f t="shared" ref="G8:G16" si="1">F8/D8</f>
         <v>1.0030975143403442</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H8" s="25">
         <v>36581376</v>
       </c>
-      <c r="I7" s="24">
-        <f t="shared" ref="I7:I14" si="2">H7/D7</f>
+      <c r="I8" s="23">
+        <f t="shared" ref="I8:I15" si="2">H8/D8</f>
         <v>1.0245889101338452</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="26">
+      <c r="K8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8">
+        <v>100000000</v>
+      </c>
+      <c r="M8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N8">
+        <v>10.05151787</v>
+      </c>
+      <c r="O8">
+        <v>0.65293832900000004</v>
+      </c>
+      <c r="P8" s="31">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="Q8">
+        <v>48710451.200000003</v>
+      </c>
+      <c r="R8">
+        <v>94002.976909999998</v>
+      </c>
+      <c r="S8" s="31">
+        <v>1.9E-3</v>
+      </c>
+      <c r="T8">
+        <v>9.7232935430000005</v>
+      </c>
+      <c r="U8">
+        <v>10.82374096</v>
+      </c>
+      <c r="V8">
+        <v>10.670188189999999</v>
+      </c>
+      <c r="W8">
+        <v>9.6842997069999992</v>
+      </c>
+      <c r="X8">
+        <v>9.356066942</v>
+      </c>
+      <c r="Y8">
+        <v>48549888</v>
+      </c>
+      <c r="Z8">
+        <v>48787456</v>
+      </c>
+      <c r="AA8">
+        <v>48709632</v>
+      </c>
+      <c r="AB8">
+        <v>48746496</v>
+      </c>
+      <c r="AC8">
+        <v>48758784</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="25">
         <v>1000000</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C9" s="20">
         <f t="shared" si="0"/>
         <v>1.25</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D9" s="25">
         <v>36220928</v>
       </c>
-      <c r="E8" s="23">
-        <f>D8/(1.3*B8/8)</f>
+      <c r="E9" s="22">
+        <f>D9/(1.3*B9/8)</f>
         <v>222.89801846153847</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F9" s="25">
         <v>36869461.333333299</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G9" s="23">
         <f t="shared" si="1"/>
         <v>1.0179049342229249</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H9" s="25">
         <v>43801258.666666597</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I9" s="23">
         <f t="shared" si="2"/>
         <v>1.2092804101172283</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="26">
+      <c r="K9" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9">
+        <v>200000000</v>
+      </c>
+      <c r="M9" t="s">
+        <v>48</v>
+      </c>
+      <c r="N9">
+        <v>21.308080289999999</v>
+      </c>
+      <c r="O9">
+        <v>0.58744498700000003</v>
+      </c>
+      <c r="P9" s="31">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Q9">
+        <v>61186048</v>
+      </c>
+      <c r="R9">
+        <v>69390.640520000001</v>
+      </c>
+      <c r="S9" s="31">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="T9">
+        <v>20.574271199999998</v>
+      </c>
+      <c r="U9">
+        <v>20.976147409999999</v>
+      </c>
+      <c r="V9">
+        <v>22.13692498</v>
+      </c>
+      <c r="W9">
+        <v>21.51781845</v>
+      </c>
+      <c r="X9">
+        <v>21.33523941</v>
+      </c>
+      <c r="Y9">
+        <v>61157376</v>
+      </c>
+      <c r="Z9">
+        <v>61272064</v>
+      </c>
+      <c r="AA9">
+        <v>61087744</v>
+      </c>
+      <c r="AB9">
+        <v>61190144</v>
+      </c>
+      <c r="AC9">
+        <v>61222912</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A10" s="6"/>
+      <c r="B10" s="25">
         <v>10000000</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C10" s="20">
         <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D10" s="25">
         <v>40737450.666666597</v>
       </c>
-      <c r="E9" s="23">
-        <f>D9/(1.3*B9/8)</f>
+      <c r="E10" s="22">
+        <f>D10/(1.3*B10/8)</f>
         <v>25.069200410256368</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F10" s="25">
         <v>47209130.666666597</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G10" s="23">
         <f t="shared" si="1"/>
         <v>1.158863156483561</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H10" s="25">
         <v>126040746.666666</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I10" s="23">
         <f t="shared" si="2"/>
         <v>3.0939772765358335</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="26">
+      <c r="K10" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10">
+        <v>300000000</v>
+      </c>
+      <c r="M10" t="s">
+        <v>48</v>
+      </c>
+      <c r="N10">
+        <v>32.488548989999998</v>
+      </c>
+      <c r="O10">
+        <v>0.81739208100000005</v>
+      </c>
+      <c r="P10" s="31">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="Q10">
+        <v>73764864</v>
+      </c>
+      <c r="R10">
+        <v>67490.844889999993</v>
+      </c>
+      <c r="S10" s="31">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="T10">
+        <v>31.30861449</v>
+      </c>
+      <c r="U10">
+        <v>33.44905043</v>
+      </c>
+      <c r="V10">
+        <v>32.473364830000001</v>
+      </c>
+      <c r="W10">
+        <v>32.199681759999997</v>
+      </c>
+      <c r="X10">
+        <v>33.012033459999998</v>
+      </c>
+      <c r="Y10">
+        <v>73670656</v>
+      </c>
+      <c r="Z10">
+        <v>73768960</v>
+      </c>
+      <c r="AA10">
+        <v>73854976</v>
+      </c>
+      <c r="AB10">
+        <v>73789440</v>
+      </c>
+      <c r="AC10">
+        <v>73740288</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A11" s="6"/>
+      <c r="B11" s="25">
         <v>100000000</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C11" s="20">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D11" s="25">
         <v>93503488</v>
       </c>
-      <c r="E10" s="23">
-        <f>D10/(1.3*B10/8)</f>
+      <c r="E11" s="22">
+        <f>D11/(1.3*B11/8)</f>
         <v>5.7540608000000004</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F11" s="25">
         <v>178421760</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G11" s="23">
         <f t="shared" si="1"/>
         <v>1.9081829332398808</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H11" s="25">
         <v>980206933.33333302</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I11" s="23">
         <f t="shared" si="2"/>
         <v>10.483105542900528</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="14"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="27"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="K11" t="s">
+        <v>50</v>
+      </c>
+      <c r="L11">
+        <v>50000000</v>
+      </c>
+      <c r="M11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N11">
+        <v>8.354029894</v>
+      </c>
+      <c r="O11">
+        <v>0.16338562400000001</v>
+      </c>
+      <c r="P11" s="31">
+        <v>0.02</v>
+      </c>
+      <c r="Q11">
+        <v>86323200</v>
+      </c>
+      <c r="R11">
+        <v>107943.3949</v>
+      </c>
+      <c r="S11" s="31">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="T11">
+        <v>8.2560346130000006</v>
+      </c>
+      <c r="U11">
+        <v>8.2239623070000007</v>
+      </c>
+      <c r="V11">
+        <v>8.5382425790000003</v>
+      </c>
+      <c r="W11">
+        <v>8.5265588759999993</v>
+      </c>
+      <c r="X11">
+        <v>8.2253510950000006</v>
+      </c>
+      <c r="Y11">
+        <v>86245376</v>
+      </c>
+      <c r="Z11">
+        <v>86335488</v>
+      </c>
+      <c r="AA11">
+        <v>86478848</v>
+      </c>
+      <c r="AB11">
+        <v>86355968</v>
+      </c>
+      <c r="AC11">
+        <v>86200320</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B12" s="14"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="26"/>
+      <c r="K12" t="s">
+        <v>50</v>
+      </c>
+      <c r="L12">
+        <v>100000000</v>
+      </c>
+      <c r="M12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N12">
+        <v>16.752499149999998</v>
+      </c>
+      <c r="O12">
+        <v>0.63200704699999999</v>
+      </c>
+      <c r="P12" s="31">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="Q12">
+        <v>136311603.19999999</v>
+      </c>
+      <c r="R12">
+        <v>52805.049939999997</v>
+      </c>
+      <c r="S12" s="31">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="T12">
+        <v>16.551253079999999</v>
+      </c>
+      <c r="U12">
+        <v>16.078412060000002</v>
+      </c>
+      <c r="V12">
+        <v>16.64575696</v>
+      </c>
+      <c r="W12">
+        <v>17.795446399999999</v>
+      </c>
+      <c r="X12">
+        <v>16.691627260000001</v>
+      </c>
+      <c r="Y12">
+        <v>136368128</v>
+      </c>
+      <c r="Z12">
+        <v>136232960</v>
+      </c>
+      <c r="AA12">
+        <v>136335360</v>
+      </c>
+      <c r="AB12">
+        <v>136335360</v>
+      </c>
+      <c r="AC12">
+        <v>136286208</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B13" s="14">
         <v>50000000</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C13" s="11">
         <f t="shared" si="0"/>
         <v>62.5</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D13" s="14">
         <v>42455040</v>
       </c>
-      <c r="E12" s="12">
-        <f>D12/(B12/8)</f>
+      <c r="E13" s="12">
+        <f>D13/(B13/8)</f>
         <v>6.7928063999999999</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F13" s="14">
         <v>86323200</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G13" s="26">
         <f t="shared" si="1"/>
         <v>2.0332850940665703</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H13" s="14">
         <v>436184678.39999998</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I13" s="26">
         <f t="shared" si="2"/>
         <v>10.274037626628076</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="14">
+      <c r="K13" t="s">
+        <v>50</v>
+      </c>
+      <c r="L13">
+        <v>200000000</v>
+      </c>
+      <c r="M13" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13">
+        <v>34.964457080000003</v>
+      </c>
+      <c r="O13">
+        <v>2.0686283589999999</v>
+      </c>
+      <c r="P13" s="31">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="Q13">
+        <v>236213043.19999999</v>
+      </c>
+      <c r="R13">
+        <v>20965.75921</v>
+      </c>
+      <c r="S13" s="31">
+        <v>1E-4</v>
+      </c>
+      <c r="T13">
+        <v>32.332689999999999</v>
+      </c>
+      <c r="U13">
+        <v>36.030251499999999</v>
+      </c>
+      <c r="V13">
+        <v>33.840595720000003</v>
+      </c>
+      <c r="W13">
+        <v>37.75403833</v>
+      </c>
+      <c r="X13">
+        <v>34.864709849999997</v>
+      </c>
+      <c r="Y13">
+        <v>236236800</v>
+      </c>
+      <c r="Z13">
+        <v>236195840</v>
+      </c>
+      <c r="AA13">
+        <v>236216320</v>
+      </c>
+      <c r="AB13">
+        <v>236187648</v>
+      </c>
+      <c r="AC13">
+        <v>236228608</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B14" s="14">
         <v>100000000</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C14" s="11">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D14" s="14">
         <v>48710451.200000003</v>
       </c>
-      <c r="E13" s="12">
-        <f>D13/(B13/8)</f>
+      <c r="E14" s="12">
+        <f>D14/(B14/8)</f>
         <v>3.8968360960000004</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F14" s="14">
         <v>136311603.19999999</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G14" s="26">
         <f t="shared" si="1"/>
         <v>2.7984056776710782</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H14" s="14">
         <v>836188569.60000002</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I14" s="26">
         <f t="shared" si="2"/>
         <v>17.166512503994213</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="14">
+      <c r="K14" t="s">
+        <v>50</v>
+      </c>
+      <c r="L14">
+        <v>300000000</v>
+      </c>
+      <c r="M14" t="s">
+        <v>48</v>
+      </c>
+      <c r="N14">
+        <v>50.554069900000002</v>
+      </c>
+      <c r="O14">
+        <v>1.0787839450000001</v>
+      </c>
+      <c r="P14" s="31">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="Q14">
+        <v>336267673.60000002</v>
+      </c>
+      <c r="R14">
+        <v>103928.68550000001</v>
+      </c>
+      <c r="S14" s="31">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="T14">
+        <v>51.993207689999998</v>
+      </c>
+      <c r="U14">
+        <v>51.310749530000002</v>
+      </c>
+      <c r="V14">
+        <v>50.211251500000003</v>
+      </c>
+      <c r="W14">
+        <v>49.925135849999997</v>
+      </c>
+      <c r="X14">
+        <v>49.330004930000001</v>
+      </c>
+      <c r="Y14">
+        <v>336379904</v>
+      </c>
+      <c r="Z14">
+        <v>336375808</v>
+      </c>
+      <c r="AA14">
+        <v>336191488</v>
+      </c>
+      <c r="AB14">
+        <v>336158720</v>
+      </c>
+      <c r="AC14">
+        <v>336232448</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B15" s="14">
         <v>200000000</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C15" s="11">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D15" s="14">
         <v>61186048</v>
       </c>
-      <c r="E14" s="12">
-        <f>D14/(B14/8)</f>
+      <c r="E15" s="12">
+        <f>D15/(B15/8)</f>
         <v>2.4474419200000002</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F15" s="14">
         <v>236213043.19999999</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G15" s="26">
         <f t="shared" si="1"/>
         <v>3.8605703574775738</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H15" s="14">
         <v>1636187340.8</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I15" s="26">
         <f t="shared" si="2"/>
         <v>26.741183558709331</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="14">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B16" s="14">
         <v>300000000</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C16" s="11">
         <f t="shared" si="0"/>
         <v>375</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D16" s="14">
         <v>73764864</v>
       </c>
-      <c r="E15" s="12">
-        <f>D15/(B15/8)</f>
+      <c r="E16" s="12">
+        <f>D16/(B16/8)</f>
         <v>1.96706304</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F16" s="14">
         <v>336267673.60000002</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G16" s="26">
         <f t="shared" si="1"/>
         <v>4.5586429007718365</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H16" s="14">
         <v>2436223795.1999998</v>
       </c>
-      <c r="I15" s="27">
-        <f>H15/D15</f>
+      <c r="I16" s="26">
+        <f>H16/D16</f>
         <v>33.026886556721635</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+    <row r="18" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="29" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="7" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B19" s="8" t="s">
+    <row r="20" spans="1:9" s="7" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B20" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C20" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D20" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E20" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F20" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G20" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H20" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I20" s="8" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="10">
-        <v>50000000</v>
-      </c>
-      <c r="C20" s="11">
-        <f>B20/8/10^6</f>
-        <v>6.25</v>
-      </c>
-      <c r="D20" s="12">
-        <f>D12/10^6</f>
-        <v>42.455039999999997</v>
-      </c>
-      <c r="E20" s="13">
-        <f>D20/C20</f>
-        <v>6.7928063999999999</v>
-      </c>
-      <c r="F20" s="12">
-        <f>F12/10^6</f>
-        <v>86.3232</v>
-      </c>
-      <c r="G20" s="13">
-        <f t="shared" ref="G20:G23" si="3">F20/D20</f>
-        <v>2.0332850940665703</v>
-      </c>
-      <c r="H20" s="12">
-        <f>H12/10^6</f>
-        <v>436.1846784</v>
-      </c>
-      <c r="I20" s="13">
-        <f t="shared" ref="I20:I22" si="4">H20/D20</f>
-        <v>10.274037626628076</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B21" s="10">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="C21" s="11">
-        <f t="shared" ref="C21:C23" si="5">B21/8/10^6</f>
-        <v>12.5</v>
+        <f>B21/8/10^6</f>
+        <v>6.25</v>
       </c>
       <c r="D21" s="12">
         <f>D13/10^6</f>
-        <v>48.710451200000001</v>
-      </c>
-      <c r="E21" s="13">
-        <f t="shared" ref="E21:E23" si="6">D21/C21</f>
-        <v>3.8968360959999999</v>
+        <v>42.455039999999997</v>
+      </c>
+      <c r="E21" s="28">
+        <f>D21/C21</f>
+        <v>6.7928063999999999</v>
       </c>
       <c r="F21" s="12">
         <f>F13/10^6</f>
+        <v>86.3232</v>
+      </c>
+      <c r="G21" s="28">
+        <f t="shared" ref="G21:G24" si="3">F21/D21</f>
+        <v>2.0332850940665703</v>
+      </c>
+      <c r="H21" s="12">
+        <f>H13/10^6</f>
+        <v>436.1846784</v>
+      </c>
+      <c r="I21" s="28">
+        <f t="shared" ref="I21:I23" si="4">H21/D21</f>
+        <v>10.274037626628076</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="C22" s="11">
+        <f t="shared" ref="C22:C24" si="5">B22/8/10^6</f>
+        <v>12.5</v>
+      </c>
+      <c r="D22" s="12">
+        <f>D14/10^6</f>
+        <v>48.710451200000001</v>
+      </c>
+      <c r="E22" s="28">
+        <f t="shared" ref="E22:E24" si="6">D22/C22</f>
+        <v>3.8968360959999999</v>
+      </c>
+      <c r="F22" s="12">
+        <f>F14/10^6</f>
         <v>136.31160319999998</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G22" s="28">
         <f t="shared" si="3"/>
         <v>2.7984056776710782</v>
       </c>
-      <c r="H21" s="12">
-        <f>H13/10^6</f>
+      <c r="H22" s="12">
+        <f>H14/10^6</f>
         <v>836.18856960000005</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I22" s="28">
         <f t="shared" si="4"/>
         <v>17.166512503994216</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="10">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="10">
         <v>200000000</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C23" s="11">
         <f t="shared" si="5"/>
         <v>25</v>
       </c>
-      <c r="D22" s="12">
-        <f>D14/10^6</f>
+      <c r="D23" s="12">
+        <f>D15/10^6</f>
         <v>61.186048</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E23" s="28">
         <f t="shared" si="6"/>
         <v>2.4474419200000002</v>
       </c>
-      <c r="F22" s="12">
-        <f>F14/10^6</f>
+      <c r="F23" s="12">
+        <f>F15/10^6</f>
         <v>236.21304319999999</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G23" s="28">
         <f t="shared" si="3"/>
         <v>3.8605703574775738</v>
       </c>
-      <c r="H22" s="12">
-        <f>H14/10^6</f>
+      <c r="H23" s="12">
+        <f>H15/10^6</f>
         <v>1636.1873407999999</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I23" s="28">
         <f t="shared" si="4"/>
         <v>26.741183558709331</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B23" s="10">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="10">
         <v>300000000</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C24" s="11">
         <f t="shared" si="5"/>
         <v>37.5</v>
       </c>
-      <c r="D23" s="12">
-        <f>D15/10^6</f>
+      <c r="D24" s="12">
+        <f>D16/10^6</f>
         <v>73.764864000000003</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E24" s="28">
         <f t="shared" si="6"/>
         <v>1.96706304</v>
       </c>
-      <c r="F23" s="12">
-        <f>F15/10^6</f>
+      <c r="F24" s="12">
+        <f>F16/10^6</f>
         <v>336.26767360000002</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G24" s="28">
         <f t="shared" si="3"/>
         <v>4.5586429007718365</v>
       </c>
-      <c r="H23" s="12">
-        <f>H15/10^6</f>
+      <c r="H24" s="12">
+        <f>H16/10^6</f>
         <v>2436.2237951999996</v>
       </c>
-      <c r="I23" s="13">
-        <f>H23/D23</f>
+      <c r="I24" s="28">
+        <f>H24/D24</f>
         <v>33.026886556721635</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="E24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="I24" s="1"/>
-    </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="3"/>
+      <c r="C25" s="4"/>
+      <c r="E25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="17">
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="16">
         <f>36200000/10^6</f>
         <v>36.200000000000003</v>
       </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="13"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="13"/>
       <c r="H26" s="14"/>
       <c r="I26" s="13"/>
     </row>
-    <row r="27" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B27" s="8" t="s">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="13"/>
+    </row>
+    <row r="28" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C28" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D28" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E28" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F28" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G28" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H28" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I28" s="8" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="10">
-        <v>50000000</v>
-      </c>
-      <c r="C28" s="11">
-        <f>B28/8/10^6</f>
-        <v>6.25</v>
-      </c>
-      <c r="D28" s="12">
-        <f>D20-$G$25</f>
-        <v>6.2550399999999939</v>
-      </c>
-      <c r="E28" s="15">
-        <f>D28/$C20</f>
-        <v>1.000806399999999</v>
-      </c>
-      <c r="F28" s="12">
-        <f>F20-$G$25</f>
-        <v>50.123199999999997</v>
-      </c>
-      <c r="G28" s="15">
-        <f t="shared" ref="G28:G31" si="7">F28/D28</f>
-        <v>8.0132501151071853</v>
-      </c>
-      <c r="H28" s="12">
-        <f>H20-$G$25</f>
-        <v>399.98467840000001</v>
-      </c>
-      <c r="I28" s="15">
-        <f t="shared" ref="I28:I31" si="8">H28/D28</f>
-        <v>63.945982503709075</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B29" s="10">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="C29" s="11">
-        <f t="shared" ref="C29:C31" si="9">B29/8/10^6</f>
-        <v>12.5</v>
+        <f>B29/8/10^6</f>
+        <v>6.25</v>
       </c>
       <c r="D29" s="12">
-        <f>D21-$G$25</f>
-        <v>12.510451199999999</v>
+        <f>D21-$G$26</f>
+        <v>6.2550399999999939</v>
       </c>
       <c r="E29" s="15">
         <f>D29/$C21</f>
+        <v>1.000806399999999</v>
+      </c>
+      <c r="F29" s="12">
+        <f>F21-$G$26</f>
+        <v>50.123199999999997</v>
+      </c>
+      <c r="G29" s="15">
+        <f t="shared" ref="G29:G32" si="7">F29/D29</f>
+        <v>8.0132501151071853</v>
+      </c>
+      <c r="H29" s="12">
+        <f>H21-$G$26</f>
+        <v>399.98467840000001</v>
+      </c>
+      <c r="I29" s="15">
+        <f t="shared" ref="I29:I32" si="8">H29/D29</f>
+        <v>63.945982503709075</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="C30" s="11">
+        <f t="shared" ref="C30:C32" si="9">B30/8/10^6</f>
+        <v>12.5</v>
+      </c>
+      <c r="D30" s="12">
+        <f>D22-$G$26</f>
+        <v>12.510451199999999</v>
+      </c>
+      <c r="E30" s="15">
+        <f>D30/$C22</f>
         <v>1.0008360959999998</v>
       </c>
-      <c r="F29" s="12">
-        <f>F21-$G$25</f>
+      <c r="F30" s="12">
+        <f>F22-$G$26</f>
         <v>100.11160319999998</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G30" s="15">
         <f t="shared" si="7"/>
         <v>8.0022376171372613</v>
       </c>
-      <c r="H29" s="12">
-        <f>H21-$G$25</f>
+      <c r="H30" s="12">
+        <f>H22-$G$26</f>
         <v>799.98856960000001</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I30" s="15">
         <f t="shared" si="8"/>
         <v>63.945620890156235</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="10">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="10">
         <v>200000000</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C31" s="11">
         <f t="shared" si="9"/>
         <v>25</v>
       </c>
-      <c r="D30" s="12">
-        <f>D22-$G$25</f>
+      <c r="D31" s="12">
+        <f>D23-$G$26</f>
         <v>24.986047999999997</v>
       </c>
-      <c r="E30" s="15">
-        <f>D30/$C22</f>
+      <c r="E31" s="15">
+        <f>D31/$C23</f>
         <v>0.99944191999999987</v>
       </c>
-      <c r="F30" s="12">
-        <f>F22-$G$25</f>
+      <c r="F31" s="12">
+        <f>F23-$G$26</f>
         <v>200.01304319999997</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G31" s="15">
         <f t="shared" si="7"/>
         <v>8.0049891523461412</v>
       </c>
-      <c r="H30" s="12">
-        <f>H22-$G$25</f>
+      <c r="H31" s="12">
+        <f>H23-$G$26</f>
         <v>1599.9873407999999</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I31" s="15">
         <f t="shared" si="8"/>
         <v>64.035230413389101</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="10">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B32" s="10">
         <v>300000000</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C32" s="11">
         <f t="shared" si="9"/>
         <v>37.5</v>
       </c>
-      <c r="D31" s="12">
-        <f>D23-$G$25</f>
+      <c r="D32" s="12">
+        <f>D24-$G$26</f>
         <v>37.564864</v>
       </c>
-      <c r="E31" s="15">
-        <f>D31/$C23</f>
+      <c r="E32" s="15">
+        <f>D32/$C24</f>
         <v>1.0017297066666666</v>
       </c>
-      <c r="F31" s="12">
-        <f>F23-$G$25</f>
+      <c r="F32" s="12">
+        <f>F24-$G$26</f>
         <v>300.06767360000003</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G32" s="15">
         <f t="shared" si="7"/>
         <v>7.9879877536625727</v>
       </c>
-      <c r="H31" s="12">
-        <f>H23-$G$25</f>
+      <c r="H32" s="12">
+        <f>H24-$G$26</f>
         <v>2400.0237951999998</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I32" s="15">
         <f t="shared" si="8"/>
         <v>63.890123366345733</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K35" t="s">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K36" t="s">
         <v>21</v>
       </c>
-      <c r="L35" t="s">
+      <c r="L36" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J36" t="s">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" t="s">
+        <v>52</v>
+      </c>
+      <c r="J37" t="s">
         <v>20</v>
       </c>
-      <c r="K36" s="2">
-        <f>D31</f>
+      <c r="K37" s="2">
+        <f>D32</f>
         <v>37.564864</v>
       </c>
-      <c r="L36" s="1">
+      <c r="L37" s="1">
         <v>4.7516013145446703</v>
       </c>
-      <c r="M36" s="1">
+      <c r="M37" s="1">
         <v>10.0515178680419</v>
       </c>
-      <c r="N36" s="1">
+      <c r="N37" s="1">
         <v>21.308080291747999</v>
       </c>
-      <c r="O36" s="1">
+      <c r="O37" s="1">
         <v>32.488548994064303</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J37" t="s">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C38" t="str">
+        <f>K7</f>
+        <v>serial_bitarray_sieve_no_return</v>
+      </c>
+      <c r="D38" s="35">
+        <f>D29</f>
+        <v>6.2550399999999939</v>
+      </c>
+      <c r="E38" s="2">
+        <f>N7</f>
+        <v>4.7516013150000003</v>
+      </c>
+      <c r="J38" t="s">
         <v>23</v>
       </c>
-      <c r="K37" s="2">
-        <f>F31</f>
+      <c r="K38" s="2">
+        <f>F32</f>
         <v>300.06767360000003</v>
       </c>
-      <c r="L37" s="1">
+      <c r="L38" s="1">
         <v>8.3540298938751203</v>
       </c>
-      <c r="M37" s="1">
+      <c r="M38" s="1">
         <v>16.752499151229799</v>
       </c>
-      <c r="N37" s="1">
+      <c r="N38" s="1">
         <v>34.964457082748403</v>
       </c>
-      <c r="O37" s="1">
+      <c r="O38" s="1">
         <v>50.554069900512602</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J38" t="s">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C39" t="str">
+        <f t="shared" ref="C39:C42" si="10">K8</f>
+        <v>serial_bitarray_sieve_no_return</v>
+      </c>
+      <c r="D39" s="35">
+        <f t="shared" ref="D39:D41" si="11">D30</f>
+        <v>12.510451199999999</v>
+      </c>
+      <c r="E39" s="2">
+        <f t="shared" ref="E39:E42" si="12">N8</f>
+        <v>10.05151787</v>
+      </c>
+      <c r="J39" t="s">
         <v>24</v>
       </c>
-      <c r="K38" s="2">
-        <f>H31</f>
+      <c r="K39" s="2">
+        <f>H32</f>
         <v>2400.0237951999998</v>
       </c>
-      <c r="L38" s="1">
+      <c r="L39" s="1">
         <v>6.9352396965026797</v>
       </c>
-      <c r="M38" s="1">
+      <c r="M39" s="1">
         <v>16.425710391998201</v>
       </c>
-      <c r="N38" s="1">
+      <c r="N39" s="1">
         <v>33.938910865783598</v>
       </c>
-      <c r="O38" s="1">
+      <c r="O39" s="1">
         <v>51.218771839141802</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K39" s="2"/>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C40" t="str">
+        <f t="shared" si="10"/>
+        <v>serial_bitarray_sieve_no_return</v>
+      </c>
+      <c r="D40" s="35">
+        <f t="shared" si="11"/>
+        <v>24.986047999999997</v>
+      </c>
+      <c r="E40" s="2">
+        <f t="shared" si="12"/>
+        <v>21.308080289999999</v>
+      </c>
+      <c r="K40" s="2"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K41" t="s">
+      <c r="C41" t="str">
+        <f t="shared" si="10"/>
+        <v>serial_bitarray_sieve_no_return</v>
+      </c>
+      <c r="D41" s="35">
+        <f t="shared" si="11"/>
+        <v>37.564864</v>
+      </c>
+      <c r="E41" s="2">
+        <f t="shared" si="12"/>
+        <v>32.488548989999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C42" t="str">
+        <f t="shared" si="10"/>
+        <v>serial_bool_sieve_no_return</v>
+      </c>
+      <c r="D42" s="35">
+        <f>F29</f>
+        <v>50.123199999999997</v>
+      </c>
+      <c r="E42" s="2">
+        <f t="shared" si="12"/>
+        <v>8.354029894</v>
+      </c>
+      <c r="J42" s="14"/>
+      <c r="K42" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="L42" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="M42" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="N42" s="10">
+        <v>200000000</v>
+      </c>
+      <c r="O42" s="10">
+        <v>300000000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="C43" t="str">
+        <f t="shared" ref="C43:C45" si="13">K12</f>
+        <v>serial_bool_sieve_no_return</v>
+      </c>
+      <c r="D43" s="35">
+        <f t="shared" ref="D43:D45" si="14">F30</f>
+        <v>100.11160319999998</v>
+      </c>
+      <c r="E43" s="2">
+        <f t="shared" ref="E43:E45" si="15">N12</f>
+        <v>16.752499149999998</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K43" s="9" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J42" t="s">
+      <c r="L43" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="M43" s="34"/>
+      <c r="N43" s="34"/>
+      <c r="O43" s="34"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C44" t="str">
+        <f t="shared" si="13"/>
+        <v>serial_bool_sieve_no_return</v>
+      </c>
+      <c r="D44" s="35">
+        <f t="shared" si="14"/>
+        <v>200.01304319999997</v>
+      </c>
+      <c r="E44" s="2">
+        <f t="shared" si="15"/>
+        <v>34.964457080000003</v>
+      </c>
+      <c r="J44" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="K42" s="1">
-        <f>K36/K$36</f>
+      <c r="K44" s="33">
+        <f>K37/K$37</f>
         <v>1</v>
       </c>
-      <c r="L42">
-        <f t="shared" ref="L42:O42" si="10">L36/L$36</f>
+      <c r="L44" s="14">
+        <f>L37/L$37</f>
         <v>1</v>
       </c>
-      <c r="M42">
-        <f t="shared" si="10"/>
+      <c r="M44" s="14">
+        <f>M37/M$37</f>
         <v>1</v>
       </c>
-      <c r="N42">
-        <f t="shared" si="10"/>
+      <c r="N44" s="14">
+        <f>N37/N$37</f>
         <v>1</v>
       </c>
-      <c r="O42">
-        <f t="shared" si="10"/>
+      <c r="O44" s="14">
+        <f>O37/O$37</f>
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J43" t="s">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C45" t="str">
+        <f t="shared" si="13"/>
+        <v>serial_bool_sieve_no_return</v>
+      </c>
+      <c r="D45" s="35">
+        <f t="shared" si="14"/>
+        <v>300.06767360000003</v>
+      </c>
+      <c r="E45" s="2">
+        <f t="shared" si="15"/>
+        <v>50.554069900000002</v>
+      </c>
+      <c r="J45" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="K43" s="1">
-        <f>K37/K$36</f>
+      <c r="K45" s="12">
+        <f>K38/K$37</f>
         <v>7.9879877536625727</v>
       </c>
-      <c r="L43" s="1">
-        <f>L37/L$36</f>
+      <c r="L45" s="13">
+        <f>L$37/L38</f>
+        <v>0.56877954411300069</v>
+      </c>
+      <c r="M45" s="13">
+        <f>M$37/M38</f>
+        <v>0.60000109698880477</v>
+      </c>
+      <c r="N45" s="13">
+        <f>N$37/N38</f>
+        <v>0.6094211685117652</v>
+      </c>
+      <c r="O45" s="13">
+        <f>O$37/O38</f>
+        <v>0.64264952471679992</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C46" t="str">
+        <f>K3</f>
+        <v>serial_int_array_sieve_no_return</v>
+      </c>
+      <c r="D46" s="35">
+        <f>H29</f>
+        <v>399.98467840000001</v>
+      </c>
+      <c r="E46" s="2">
+        <f>N3</f>
+        <v>6.9352396970000001</v>
+      </c>
+      <c r="J46" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K46" s="12">
+        <f>K39/K$37</f>
+        <v>63.890123366345733</v>
+      </c>
+      <c r="L46" s="13">
+        <f>L$37/L39</f>
+        <v>0.68513872951511967</v>
+      </c>
+      <c r="M46" s="13">
+        <f>M$37/M39</f>
+        <v>0.61193809145317124</v>
+      </c>
+      <c r="N46" s="13">
+        <f>N$37/N39</f>
+        <v>0.62783630199607554</v>
+      </c>
+      <c r="O46" s="13">
+        <f>O$37/O39</f>
+        <v>0.63430941093429904</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C47" t="str">
+        <f t="shared" ref="C47:C49" si="16">K4</f>
+        <v>serial_int_array_sieve_no_return</v>
+      </c>
+      <c r="D47" s="35">
+        <f t="shared" ref="D47:D49" si="17">H30</f>
+        <v>799.98856960000001</v>
+      </c>
+      <c r="E47" s="2">
+        <f t="shared" ref="E47:E49" si="18">N4</f>
+        <v>16.425710389999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C48" t="str">
+        <f t="shared" si="16"/>
+        <v>serial_int_array_sieve_no_return</v>
+      </c>
+      <c r="D48" s="35">
+        <f t="shared" si="17"/>
+        <v>1599.9873407999999</v>
+      </c>
+      <c r="E48" s="2">
+        <f t="shared" si="18"/>
+        <v>33.938910870000001</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C49" t="str">
+        <f t="shared" si="16"/>
+        <v>serial_int_array_sieve_no_return</v>
+      </c>
+      <c r="D49" s="35">
+        <f t="shared" si="17"/>
+        <v>2400.0237951999998</v>
+      </c>
+      <c r="E49" s="2">
+        <f t="shared" si="18"/>
+        <v>51.218771840000002</v>
+      </c>
+      <c r="L49">
+        <f>1/L45</f>
         <v>1.7581504298989483</v>
       </c>
-      <c r="M43" s="1">
-        <f>M37/M$36</f>
+      <c r="M49">
+        <f t="shared" ref="M49:O50" si="19">1/M45</f>
         <v>1.6666636194811135</v>
       </c>
-      <c r="N43" s="1">
-        <f>N37/N$36</f>
+      <c r="N49">
+        <f t="shared" si="19"/>
         <v>1.6409013202512253</v>
       </c>
-      <c r="O43" s="1">
-        <f>O37/O$36</f>
+      <c r="O49">
+        <f t="shared" si="19"/>
         <v>1.5560581024947864</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J44" t="s">
-        <v>24</v>
-      </c>
-      <c r="K44" s="1">
-        <f>K38/K$36</f>
-        <v>63.890123366345733</v>
-      </c>
-      <c r="L44" s="1">
-        <f>L38/L$36</f>
-        <v>1.459558417764109</v>
-      </c>
-      <c r="M44" s="1">
-        <f>M38/M$36</f>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="L50">
+        <f>1/L46</f>
+        <v>1.4595584177641092</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="19"/>
         <v>1.6341522352780768</v>
       </c>
-      <c r="N44" s="1">
-        <f>N38/N$36</f>
-        <v>1.59277186875099</v>
-      </c>
-      <c r="O44" s="1">
-        <f>O38/O$36</f>
-        <v>1.5765176785365063</v>
+      <c r="N50">
+        <f t="shared" si="19"/>
+        <v>1.5927718687509897</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="19"/>
+        <v>1.5765176785365065</v>
+      </c>
+    </row>
+    <row r="66" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C66" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" t="s">
+        <v>7</v>
+      </c>
+      <c r="E66" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C67">
+        <v>50000000</v>
+      </c>
+      <c r="D67">
+        <v>6.25</v>
+      </c>
+      <c r="E67" s="2">
+        <v>6.2550399999999939</v>
+      </c>
+      <c r="F67" s="2">
+        <v>50.123199999999997</v>
+      </c>
+      <c r="G67" s="2">
+        <v>399.98467840000001</v>
+      </c>
+    </row>
+    <row r="68" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C68">
+        <v>100000000</v>
+      </c>
+      <c r="D68">
+        <v>12.5</v>
+      </c>
+      <c r="E68" s="2">
+        <v>12.510451199999999</v>
+      </c>
+      <c r="F68" s="2">
+        <v>100.11160319999998</v>
+      </c>
+      <c r="G68" s="2">
+        <v>799.98856960000001</v>
+      </c>
+    </row>
+    <row r="69" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C69">
+        <v>200000000</v>
+      </c>
+      <c r="D69">
+        <v>25</v>
+      </c>
+      <c r="E69" s="2">
+        <v>24.986047999999997</v>
+      </c>
+      <c r="F69" s="2">
+        <v>200.01304319999997</v>
+      </c>
+      <c r="G69" s="2">
+        <v>1599.9873407999999</v>
+      </c>
+    </row>
+    <row r="70" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C70">
+        <v>300000000</v>
+      </c>
+      <c r="D70">
+        <v>37.5</v>
+      </c>
+      <c r="E70" s="2">
+        <v>37.564864</v>
+      </c>
+      <c r="F70" s="2">
+        <v>300.06767360000003</v>
+      </c>
+      <c r="G70" s="2">
+        <v>2400.0237951999998</v>
+      </c>
+    </row>
+    <row r="73" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="E73" s="2">
+        <v>64</v>
+      </c>
+      <c r="F73" s="2">
+        <v>8</v>
+      </c>
+      <c r="G73" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C74" t="s">
+        <v>6</v>
+      </c>
+      <c r="E74" t="s">
+        <v>55</v>
+      </c>
+      <c r="F74" t="s">
+        <v>56</v>
+      </c>
+      <c r="G74" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="75" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C75">
+        <v>50000000</v>
+      </c>
+      <c r="D75" s="35">
+        <f>SQRT(C75)</f>
+        <v>7071.0678118654751</v>
+      </c>
+    </row>
+    <row r="76" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C76">
+        <v>100000000</v>
+      </c>
+      <c r="D76" s="35">
+        <f t="shared" ref="D76:D78" si="20">SQRT(C76)</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="77" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C77">
+        <v>200000000</v>
+      </c>
+      <c r="D77" s="35">
+        <f t="shared" si="20"/>
+        <v>14142.13562373095</v>
+      </c>
+    </row>
+    <row r="78" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C78">
+        <v>300000000</v>
+      </c>
+      <c r="D78" s="35">
+        <f t="shared" si="20"/>
+        <v>17320.508075688773</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B25:F25"/>
+  <mergeCells count="2">
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="L43:O43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3107,7 +5543,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
